--- a/data_raw/surat keluar.xlsx
+++ b/data_raw/surat keluar.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbookair/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbookair/self-projects/in-hc/data_raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFDBCA8F-7F45-2043-8EE0-67A11A89CD3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{664549B2-A0DF-F149-8C24-6705636A53F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="1160" windowWidth="27640" windowHeight="16660" xr2:uid="{EED84C68-0AFE-DB49-B21C-6385BD8BC651}"/>
   </bookViews>
   <sheets>
     <sheet name="SURAT KELUAR" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -9805,7 +9805,7 @@
       <c r="F1008" s="2"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" sqref="F2:F250" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"PPH,KM,PPL"</formula1>
     </dataValidation>
